--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -578,10 +578,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -590,7 +590,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -735,10 +735,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -901,10 +901,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>7.6</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,72 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -715,16 +781,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -881,16 +950,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>61.54</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -926,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -956,6 +1025,190 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920057</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920063</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920035</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920036</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920046</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920048</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920062</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -79,12 +79,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -103,13 +115,19 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
   </si>
   <si>
     <t>SIERRA</t>
@@ -121,10 +139,22 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>GABRIELA ELIZABET</t>
@@ -712,16 +742,19 @@
         <v>28</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>28</v>
       </c>
-      <c r="E2">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -735,16 +768,19 @@
         <v>33</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>33</v>
       </c>
-      <c r="E3">
-        <v>33</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -758,16 +794,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -807,16 +846,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +923,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -907,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -924,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -976,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,22 +1069,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920057</v>
+        <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1050,22 +1092,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920063</v>
+        <v>21330051920102</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,16 +1115,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920035</v>
+        <v>21330051920057</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1091,21 +1133,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920063</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1114,50 +1156,50 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920046</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920048</v>
+        <v>21330051920077</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1165,16 +1207,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920062</v>
+        <v>21330051920035</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1188,16 +1230,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920065</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1206,6 +1248,98 @@
         <v>12</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920046</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920048</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920062</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920065</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -794,16 +794,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>75.76000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>84.84999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -843,10 +843,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -855,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -1012,10 +1012,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -1024,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="H6">
         <v>6.9</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -79,40 +79,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>JUSTO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TETLA</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECATL</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
   </si>
   <si>
     <t>NEGRETE</t>
@@ -121,22 +148,37 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
@@ -145,34 +187,28 @@
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
-    <t>YAZURI</t>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -823,13 +859,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -949,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -992,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1037,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,16 +1105,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920305</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1092,16 +1128,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920102</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1115,22 +1151,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920057</v>
+        <v>21330051920135</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1138,22 +1174,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920063</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1161,16 +1197,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1190,10 +1226,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1207,22 +1243,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920035</v>
+        <v>21330051920305</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1230,22 +1266,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920036</v>
+        <v>21330051920102</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1253,16 +1289,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920046</v>
+        <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1276,16 +1312,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920048</v>
+        <v>21330051920036</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1299,16 +1335,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920046</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1322,16 +1358,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920065</v>
+        <v>21330051920048</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1340,6 +1376,98 @@
         <v>12</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920057</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920065</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920067</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -79,136 +79,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
     <t>RONALDO</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
   </si>
 </sst>
 </file>
@@ -713,19 +590,19 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>92.31</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -882,19 +759,19 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -950,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1002,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1028,16 +905,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>69.23</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1051,19 +928,19 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>61.54</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,370 +982,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920109</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920135</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920140</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920077</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920305</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920035</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920036</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920046</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920048</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920057</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920065</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920067</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920141</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -79,13 +79,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>RONALDO</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -853,16 +895,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -950,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,25 +1024,140 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920147</v>
+        <v>21330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920378</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920076</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920103</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -878,7 +878,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -904,7 +904,7 @@
         <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -930,7 +930,7 @@
         <v>96.97</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -956,7 +956,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -982,7 +982,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20231.xlsx
@@ -878,7 +878,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -904,7 +904,7 @@
         <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -930,7 +930,7 @@
         <v>96.97</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -956,7 +956,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -982,7 +982,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
